--- a/event_evaluation_forms/027_menu_tasting_form--event_evaluation_forms.xlsx
+++ b/event_evaluation_forms/027_menu_tasting_form--event_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,9 +440,9 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Form Title</t>
+          <t>Your Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +543,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>presentation_rating</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Form Description</t>
+          <t>How would you rate the presentation of the dish?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>flavor_rating</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Form Category</t>
+          <t>How good was the flavor of the dish?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,41 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_tags</t>
+          <t>produce_freshness</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Form Tags</t>
+          <t>How fresh is the produce?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_image</t>
+          <t>cuisine_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Form Image</t>
+          <t>What type of cuisine does the dish belong to?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>appeal_rating</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>How much does the dish appeal to you?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>event_evaluation_form_1_1</t>
+          <t>portion_size_rating</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>How would you rate the portion size?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,41 +681,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>event_evaluation_form_1_2</t>
+          <t>have_again_rating</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>How much would you like to have it again?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>event_evaluation_form_1_3</t>
+          <t>price_range</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>What is the price range you are willing to pay for this dish?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_evaluation_form_1_4</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>How likely are you to recommend this dish to friends?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>event_evaluation_form_1_5</t>
+          <t>discount_request</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Would you like to have a discount on this dish?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_evaluation_form_1_6</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>How would you rate the overall experience?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,34 +827,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>cuisine_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>event_evaluation_forms</t>
+          <t>american</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Event Evaluation Forms</t>
+          <t>American</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>cuisine_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other_form</t>
+          <t>italian</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other Form</t>
+          <t>Italian</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cuisine_type_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cuisine_type_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>price_range_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$5-$10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>$5-$10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>price_range_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>$10-$15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>$10-$15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>price_range_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>$15-$20</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>$15-$20</t>
         </is>
       </c>
     </row>
